--- a/primeren-paten-list.xlsx
+++ b/primeren-paten-list.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J75"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -435,13 +435,13 @@
         <v>Фирма</v>
       </c>
       <c r="B3" t="str">
-        <v>BLD</v>
+        <v>БЛД ЕООД (примерни данни)</v>
       </c>
       <c r="C3" t="str">
         <v>ЕИК</v>
       </c>
       <c r="D3" t="str">
-        <v>207433903</v>
+        <v>000000000</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         <v>МОЛ</v>
       </c>
       <c r="D4" t="str">
-        <v>Димитър Бончев Савов, Христо Теодоров Илиев, Павлин Деков Петков</v>
+        <v>Управител (МОЛ)</v>
       </c>
     </row>
     <row r="5">
@@ -543,25 +543,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D10" t="str">
-        <v>MONA 5, Манастирски ливади-изток; SREDA, Манастирски ливади-изток; SLOW LIFE, Владая</v>
+        <v>AVIVA Living, Възраждане; Столична община, ул. Московска 33; ДНСК</v>
       </c>
       <c r="E10" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F10" t="str">
-        <v>Среща с клиент; Приемане на изпълнени СМР; Среща с подизпълнител</v>
+        <v>Среща с клиент; Подаване на документи</v>
       </c>
       <c r="G10">
         <v>45000</v>
       </c>
       <c r="H10">
-        <v>45049</v>
+        <v>45023</v>
       </c>
       <c r="I10">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="J10">
-        <v>2.84</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="11">
@@ -575,19 +575,19 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D11" t="str">
-        <v>SECRET GARDENS, Лозенец; Столична община, ул. Московска 33; АГКК (Кадастър)</v>
+        <v>MONA 5, Манастирски ливади-изток; SECRET GARDENS, Лозенец; Съдебна палата, бул. Витоша 2</v>
       </c>
       <c r="E11" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F11" t="str">
-        <v>Среща с клиент; Справка и съгласуване</v>
+        <v>Среща с клиент; Оглед на обект; Справка и съгласуване</v>
       </c>
       <c r="G11">
-        <v>45049</v>
+        <v>45023</v>
       </c>
       <c r="H11">
-        <v>45072</v>
+        <v>45046</v>
       </c>
       <c r="I11">
         <v>23</v>
@@ -607,25 +607,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D12" t="str">
-        <v>Посещение при клиент</v>
+        <v>UPTOWN SQUARE, Лозенец; SONATA, ул. Филип Аврамов; АГКК (Кадастър)</v>
       </c>
       <c r="E12" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F12" t="str">
-        <v>Оглед при клиент</v>
+        <v>Контрол на доставка на материали; Приемане на изпълнени СМР; Подаване на документи</v>
       </c>
       <c r="G12">
-        <v>45072</v>
+        <v>45046</v>
       </c>
       <c r="H12">
-        <v>45088</v>
+        <v>45068</v>
       </c>
       <c r="I12">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J12">
-        <v>0.93</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="13">
@@ -633,31 +633,31 @@
         <v>4</v>
       </c>
       <c r="B13" t="str">
-        <v>02.09.2026</v>
+        <v>01.09.2026</v>
       </c>
       <c r="C13" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D13" t="str">
-        <v>Столична община, ул. Московска 33; МРРБ, ул. Св. св. Кирил и Методий 17; Съдебна палата, бул. Витоша 2</v>
+        <v>Посещение при клиент</v>
       </c>
       <c r="E13" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F13" t="str">
-        <v>Подаване на документи; Получаване на документи; Справка и съгласуване</v>
+        <v>Връчване на документи на клиент</v>
       </c>
       <c r="G13">
-        <v>45088</v>
+        <v>45068</v>
       </c>
       <c r="H13">
-        <v>45104</v>
+        <v>45099</v>
       </c>
       <c r="I13">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J13">
-        <v>0.93</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="14">
@@ -671,25 +671,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D14" t="str">
-        <v>SREDA, Манастирски ливади-изток; AVIVA Living, Възраждане; ДНСК</v>
+        <v>SECRET GARDENS, Лозенец; AVIVA Living, Възраждане; Съдебна палата, бул. Витоша 2</v>
       </c>
       <c r="E14" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F14" t="str">
-        <v>Среща с подизпълнител; Приемане на изпълнени СМР; Справка и съгласуване</v>
+        <v>Оглед на обект; Контрол на доставка на материали; Подаване на документи</v>
       </c>
       <c r="G14">
-        <v>45104</v>
+        <v>45099</v>
       </c>
       <c r="H14">
-        <v>45129</v>
+        <v>45120</v>
       </c>
       <c r="I14">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J14">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="15">
@@ -703,25 +703,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D15" t="str">
-        <v>Посещение при клиент</v>
+        <v>SREDA, Манастирски ливади-изток; Съдебна палата, бул. Витоша 2; НАП, Централно управление</v>
       </c>
       <c r="E15" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F15" t="str">
-        <v>Консултация при клиент</v>
+        <v>Среща с подизпълнител; Получаване на документи; Справка и съгласуване</v>
       </c>
       <c r="G15">
-        <v>45129</v>
+        <v>45120</v>
       </c>
       <c r="H15">
-        <v>45172</v>
+        <v>45144</v>
       </c>
       <c r="I15">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="J15">
-        <v>2.49</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="16">
@@ -729,31 +729,31 @@
         <v>7</v>
       </c>
       <c r="B16" t="str">
-        <v>03.09.2026</v>
+        <v>02.09.2026</v>
       </c>
       <c r="C16" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D16" t="str">
-        <v>MONA 5, Манастирски ливади-изток; АГКК (Кадастър); ДНСК</v>
+        <v>AVIVA Living, Възраждане; Съдебна палата, бул. Витоша 2</v>
       </c>
       <c r="E16" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F16" t="str">
-        <v>Среща с подизпълнител; Получаване на документи; Справка и съгласуване</v>
+        <v>Приемане на изпълнени СМР; Подаване на документи</v>
       </c>
       <c r="G16">
-        <v>45172</v>
+        <v>45144</v>
       </c>
       <c r="H16">
-        <v>45197</v>
+        <v>45162</v>
       </c>
       <c r="I16">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J16">
-        <v>1.45</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="17">
@@ -767,25 +767,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D17" t="str">
-        <v>MONA 5, Манастирски ливади-изток; UPTOWN SQUARE, Лозенец; AVIVA Living, Възраждане</v>
+        <v>MONA 6, Манастирски ливади-изток; МРРБ, ул. Св. св. Кирил и Методий 17; Съдебна палата, бул. Витоша 2</v>
       </c>
       <c r="E17" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F17" t="str">
-        <v>Контрол на СМР; Контрол на доставка на материали; Приемане на изпълнени СМР</v>
+        <v>Контрол на СМР; Получаване на документи</v>
       </c>
       <c r="G17">
-        <v>45197</v>
+        <v>45162</v>
       </c>
       <c r="H17">
-        <v>45224</v>
+        <v>45184</v>
       </c>
       <c r="I17">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J17">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="18">
@@ -799,25 +799,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D18" t="str">
-        <v>МРРБ, ул. Св. св. Кирил и Методий 17; Съдебна палата, бул. Витоша 2; Агенция по вписванията</v>
+        <v>MONA 5, Манастирски ливади-изток; SONATA, ул. Филип Аврамов; ДНСК</v>
       </c>
       <c r="E18" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F18" t="str">
-        <v>Подаване на документи; Справка и съгласуване; Среща в администрацията</v>
+        <v>Оглед на обект; Получаване на документи</v>
       </c>
       <c r="G18">
-        <v>45224</v>
+        <v>45184</v>
       </c>
       <c r="H18">
-        <v>45243</v>
+        <v>45208</v>
       </c>
       <c r="I18">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J18">
-        <v>1.1</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="19">
@@ -825,31 +825,31 @@
         <v>10</v>
       </c>
       <c r="B19" t="str">
-        <v>04.09.2026</v>
+        <v>03.09.2026</v>
       </c>
       <c r="C19" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D19" t="str">
-        <v>SONATA, ул. Филип Аврамов; SLOW LIFE, Владая; АГКК (Кадастър)</v>
+        <v>Столична община, ул. Московска 33; МРРБ, ул. Св. св. Кирил и Методий 17; Съдебна палата, бул. Витоша 2</v>
       </c>
       <c r="E19" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F19" t="str">
-        <v>Среща с подизпълнител; Контрол на СМР; Получаване на документи</v>
+        <v>Среща в администрацията; Подаване на документи</v>
       </c>
       <c r="G19">
-        <v>45243</v>
+        <v>45208</v>
       </c>
       <c r="H19">
-        <v>45281</v>
+        <v>45224</v>
       </c>
       <c r="I19">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="J19">
-        <v>2.2</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="20">
@@ -863,25 +863,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D20" t="str">
-        <v>SECRET GARDENS, Лозенец; AVIVA Living, Възраждане; Столична община, ул. Московска 33</v>
+        <v>UPTOWN SQUARE, Лозенец; SONATA, ул. Филип Аврамов; KRISTA, Кръстова вада</v>
       </c>
       <c r="E20" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F20" t="str">
-        <v>Контрол на доставка на материали; Среща в администрацията</v>
+        <v>Приемане на изпълнени СМР; Среща с подизпълнител; Среща с клиент</v>
       </c>
       <c r="G20">
-        <v>45281</v>
+        <v>45224</v>
       </c>
       <c r="H20">
-        <v>45302</v>
+        <v>45247</v>
       </c>
       <c r="I20">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J20">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="21">
@@ -895,25 +895,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D21" t="str">
-        <v>Столична община, ул. Московска 33; Агенция по вписванията</v>
+        <v>SREDA, Манастирски ливади-изток; AVIVA Living, Възраждане; ДНСК</v>
       </c>
       <c r="E21" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F21" t="str">
-        <v>Получаване на документи; Справка и съгласуване</v>
+        <v>Оглед на обект; Контрол на доставка на материали; Справка и съгласуване</v>
       </c>
       <c r="G21">
-        <v>45302</v>
+        <v>45247</v>
       </c>
       <c r="H21">
-        <v>45318</v>
+        <v>45272</v>
       </c>
       <c r="I21">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J21">
-        <v>0.93</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="22">
@@ -921,31 +921,31 @@
         <v>13</v>
       </c>
       <c r="B22" t="str">
-        <v>07.09.2026</v>
+        <v>04.09.2026</v>
       </c>
       <c r="C22" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D22" t="str">
-        <v>MONA 5, Манастирски ливади-изток; SLOW LIFE, Владая; АГКК (Кадастър)</v>
+        <v>Посещение при клиент</v>
       </c>
       <c r="E22" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F22" t="str">
-        <v>Контрол на СМР; Оглед на обект; Подаване на документи</v>
+        <v>Оглед при клиент</v>
       </c>
       <c r="G22">
-        <v>45318</v>
+        <v>45272</v>
       </c>
       <c r="H22">
-        <v>45359</v>
+        <v>45299</v>
       </c>
       <c r="I22">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="J22">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="23">
@@ -959,25 +959,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D23" t="str">
-        <v>Посещение при клиент</v>
+        <v>SONATA, ул. Филип Аврамов; Столична община, ул. Московска 33; ДНСК</v>
       </c>
       <c r="E23" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F23" t="str">
-        <v>Среща с клиент</v>
+        <v>Оглед на обект; Среща в администрацията; Подаване на документи</v>
       </c>
       <c r="G23">
-        <v>45359</v>
+        <v>45299</v>
       </c>
       <c r="H23">
-        <v>45400</v>
+        <v>45319</v>
       </c>
       <c r="I23">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="J23">
-        <v>2.38</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="24">
@@ -985,31 +985,31 @@
         <v>15</v>
       </c>
       <c r="B24" t="str">
-        <v>08.09.2026</v>
+        <v>07.09.2026</v>
       </c>
       <c r="C24" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D24" t="str">
-        <v>MONA 5, Манастирски ливади-изток; MONA 6, Манастирски ливади-изток; SREDA, Манастирски ливади-изток</v>
+        <v>SECRET GARDENS, Лозенец; AVIVA Living, Възраждане; Столична община, ул. Московска 33</v>
       </c>
       <c r="E24" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F24" t="str">
-        <v>Оглед на обект</v>
+        <v>Приемане на изпълнени СМР; Оглед на обект; Подаване на документи</v>
       </c>
       <c r="G24">
-        <v>45400</v>
+        <v>45319</v>
       </c>
       <c r="H24">
-        <v>45428</v>
+        <v>45340</v>
       </c>
       <c r="I24">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J24">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="25">
@@ -1017,31 +1017,31 @@
         <v>16</v>
       </c>
       <c r="B25" t="str">
-        <v>08.09.2026</v>
+        <v>07.09.2026</v>
       </c>
       <c r="C25" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D25" t="str">
-        <v>MONA 6, Манастирски ливади-изток; AVIVA Living, Възраждане; ДНСК</v>
+        <v>UPTOWN SQUARE, Лозенец; Съдебна палата, бул. Витоша 2; АГКК (Кадастър)</v>
       </c>
       <c r="E25" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F25" t="str">
-        <v>Среща с подизпълнител; Приемане на изпълнени СМР; Получаване на документи</v>
+        <v>Приемане на изпълнени СМР; Подаване на документи; Получаване на документи</v>
       </c>
       <c r="G25">
-        <v>45428</v>
+        <v>45340</v>
       </c>
       <c r="H25">
-        <v>45453</v>
+        <v>45361</v>
       </c>
       <c r="I25">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J25">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="26">
@@ -1049,31 +1049,31 @@
         <v>17</v>
       </c>
       <c r="B26" t="str">
-        <v>08.09.2026</v>
+        <v>07.09.2026</v>
       </c>
       <c r="C26" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D26" t="str">
-        <v>MONA 6, Манастирски ливади-изток; UPTOWN SQUARE, Лозенец; AVIVA Living, Възраждане</v>
+        <v>Посещение при клиент</v>
       </c>
       <c r="E26" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F26" t="str">
-        <v>Среща с клиент; Оглед на обект; Приемане на изпълнени СМР</v>
+        <v>Връчване на документи на клиент</v>
       </c>
       <c r="G26">
-        <v>45453</v>
+        <v>45361</v>
       </c>
       <c r="H26">
-        <v>45480</v>
+        <v>45389</v>
       </c>
       <c r="I26">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J26">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="27">
@@ -1087,25 +1087,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D27" t="str">
-        <v>Посещение при клиент</v>
+        <v>MONA 5, Манастирски ливади-изток; SONATA, ул. Филип Аврамов; Столична община, ул. Московска 33</v>
       </c>
       <c r="E27" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F27" t="str">
-        <v>Среща с клиент</v>
+        <v>Контрол на доставка на материали; Оглед на обект; Получаване на документи</v>
       </c>
       <c r="G27">
-        <v>45480</v>
+        <v>45389</v>
       </c>
       <c r="H27">
-        <v>45505</v>
+        <v>45412</v>
       </c>
       <c r="I27">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J27">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="28">
@@ -1113,31 +1113,31 @@
         <v>19</v>
       </c>
       <c r="B28" t="str">
-        <v>09.09.2026</v>
+        <v>08.09.2026</v>
       </c>
       <c r="C28" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D28" t="str">
-        <v>SONATA, ул. Филип Аврамов; AVIVA Living, Възраждане; Съдебна палата, бул. Витоша 2</v>
+        <v>SREDA, Манастирски ливади-изток; SECRET GARDENS, Лозенец; Агенция по вписванията</v>
       </c>
       <c r="E28" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F28" t="str">
-        <v>Оглед на обект; Среща с подизпълнител; Справка и съгласуване</v>
+        <v>Приемане на изпълнени СМР; Среща с подизпълнител; Справка и съгласуване</v>
       </c>
       <c r="G28">
-        <v>45505</v>
+        <v>45412</v>
       </c>
       <c r="H28">
-        <v>45526</v>
+        <v>45437</v>
       </c>
       <c r="I28">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J28">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="29">
@@ -1145,31 +1145,31 @@
         <v>20</v>
       </c>
       <c r="B29" t="str">
-        <v>09.09.2026</v>
+        <v>08.09.2026</v>
       </c>
       <c r="C29" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D29" t="str">
-        <v>SREDA, Манастирски ливади-изток; UPTOWN SQUARE, Лозенец; SLOW LIFE, Владая</v>
+        <v>Посещение при клиент</v>
       </c>
       <c r="E29" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F29" t="str">
-        <v>Среща с клиент; Контрол на СМР; Оглед на обект</v>
+        <v>Връчване на документи на клиент</v>
       </c>
       <c r="G29">
-        <v>45526</v>
+        <v>45437</v>
       </c>
       <c r="H29">
-        <v>45575</v>
+        <v>45475</v>
       </c>
       <c r="I29">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="J29">
-        <v>2.84</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="30">
@@ -1183,25 +1183,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D30" t="str">
-        <v>MONA 6, Манастирски ливади-изток; SONATA, ул. Филип Аврамов; НАП, Централно управление</v>
+        <v>UPTOWN SQUARE, Лозенец; SONATA, ул. Филип Аврамов; АГКК (Кадастър)</v>
       </c>
       <c r="E30" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F30" t="str">
-        <v>Контрол на СМР; Среща с подизпълнител; Получаване на документи</v>
+        <v>Контрол на доставка на материали; Приемане на изпълнени СМР; Подаване на документи</v>
       </c>
       <c r="G30">
-        <v>45575</v>
+        <v>45475</v>
       </c>
       <c r="H30">
-        <v>45599</v>
+        <v>45497</v>
       </c>
       <c r="I30">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J30">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="31">
@@ -1209,31 +1209,31 @@
         <v>22</v>
       </c>
       <c r="B31" t="str">
-        <v>10.09.2026</v>
+        <v>09.09.2026</v>
       </c>
       <c r="C31" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D31" t="str">
-        <v>MONA 5, Манастирски ливади-изток; MONA 6, Манастирски ливади-изток; SLOW LIFE, Владая</v>
+        <v>UPTOWN SQUARE, Лозенец; SECRET GARDENS, Лозенец; AVIVA Living, Възраждане</v>
       </c>
       <c r="E31" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F31" t="str">
-        <v>Среща с клиент</v>
+        <v>Оглед на обект; Приемане на изпълнени СМР; Контрол на доставка на материали</v>
       </c>
       <c r="G31">
-        <v>45599</v>
+        <v>45497</v>
       </c>
       <c r="H31">
-        <v>45648</v>
+        <v>45519</v>
       </c>
       <c r="I31">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="J31">
-        <v>2.84</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="32">
@@ -1247,25 +1247,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D32" t="str">
-        <v>SLOW LIFE, Владая; АГКК (Кадастър)</v>
+        <v>SECRET GARDENS, Лозенец; НАП, Централно управление; ДНСК</v>
       </c>
       <c r="E32" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F32" t="str">
-        <v>Оглед на обект; Подаване на документи</v>
+        <v>Контрол на доставка на материали; Среща в администрацията; Справка и съгласуване</v>
       </c>
       <c r="G32">
-        <v>45648</v>
+        <v>45519</v>
       </c>
       <c r="H32">
-        <v>45691</v>
+        <v>45539</v>
       </c>
       <c r="I32">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="J32">
-        <v>2.49</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="33">
@@ -1279,25 +1279,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D33" t="str">
-        <v>MONA 6, Манастирски ливади-изток; Столична община, ул. Московска 33; Агенция по вписванията</v>
+        <v>UPTOWN SQUARE, Лозенец; KRISTA, Кръстова вада</v>
       </c>
       <c r="E33" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F33" t="str">
-        <v>Приемане на изпълнени СМР; Справка и съгласуване; Получаване на документи</v>
+        <v>Контрол на доставка на материали</v>
       </c>
       <c r="G33">
-        <v>45691</v>
+        <v>45539</v>
       </c>
       <c r="H33">
-        <v>45716</v>
+        <v>45558</v>
       </c>
       <c r="I33">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J33">
-        <v>1.45</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="34">
@@ -1305,25 +1305,25 @@
         <v>25</v>
       </c>
       <c r="B34" t="str">
-        <v>11.09.2026</v>
+        <v>14.09.2026</v>
       </c>
       <c r="C34" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D34" t="str">
-        <v>Посещение при клиент</v>
+        <v>МРРБ, ул. Св. св. Кирил и Методий 17; ДНСК</v>
       </c>
       <c r="E34" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F34" t="str">
-        <v>Консултация при клиент</v>
+        <v>Среща в администрацията; Подаване на документи</v>
       </c>
       <c r="G34">
-        <v>45716</v>
+        <v>45558</v>
       </c>
       <c r="H34">
-        <v>45731</v>
+        <v>45573</v>
       </c>
       <c r="I34">
         <v>15</v>
@@ -1349,13 +1349,13 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F35" t="str">
-        <v>Среща с подизпълнител; Получаване на документи</v>
+        <v>Контрол на доставка на материали; Приемане на изпълнени СМР; Среща в администрацията</v>
       </c>
       <c r="G35">
-        <v>45731</v>
+        <v>45573</v>
       </c>
       <c r="H35">
-        <v>45749</v>
+        <v>45591</v>
       </c>
       <c r="I35">
         <v>18</v>
@@ -1375,25 +1375,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D36" t="str">
-        <v>UPTOWN SQUARE, Лозенец; МРРБ, ул. Св. св. Кирил и Методий 17; НАП, Централно управление</v>
+        <v>KRISTA, Кръстова вада; Агенция по вписванията; АГКК (Кадастър)</v>
       </c>
       <c r="E36" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F36" t="str">
-        <v>Контрол на СМР; Среща в администрацията; Справка и съгласуване</v>
+        <v>Контрол на доставка на материали; Среща в администрацията; Подаване на документи</v>
       </c>
       <c r="G36">
-        <v>45749</v>
+        <v>45591</v>
       </c>
       <c r="H36">
-        <v>45767</v>
+        <v>45618</v>
       </c>
       <c r="I36">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J36">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="37">
@@ -1413,19 +1413,19 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F37" t="str">
-        <v>Среща с клиент</v>
+        <v>Среща с клиент на адрес</v>
       </c>
       <c r="G37">
-        <v>45767</v>
+        <v>45618</v>
       </c>
       <c r="H37">
-        <v>45784</v>
+        <v>45662</v>
       </c>
       <c r="I37">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="J37">
-        <v>0.99</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="38">
@@ -1439,25 +1439,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D38" t="str">
-        <v>SREDA, Манастирски ливади-изток; SLOW LIFE, Владая; НАП, Централно управление</v>
+        <v>UPTOWN SQUARE, Лозенец; Столична община, ул. Московска 33; ДНСК</v>
       </c>
       <c r="E38" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F38" t="str">
-        <v>Контрол на доставка на материали; Среща с клиент; Получаване на документи</v>
+        <v>Оглед на обект; Подаване на документи</v>
       </c>
       <c r="G38">
-        <v>45784</v>
+        <v>45662</v>
       </c>
       <c r="H38">
-        <v>45823</v>
+        <v>45680</v>
       </c>
       <c r="I38">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="J38">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="39">
@@ -1465,31 +1465,31 @@
         <v>30</v>
       </c>
       <c r="B39" t="str">
-        <v>15.09.2026</v>
+        <v>16.09.2026</v>
       </c>
       <c r="C39" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D39" t="str">
-        <v>MONA 6, Манастирски ливади-изток; KRISTA, Кръстова вада; Съдебна палата, бул. Витоша 2</v>
+        <v>SLOW LIFE, Владая; KRISTA, Кръстова вада; Съдебна палата, бул. Витоша 2</v>
       </c>
       <c r="E39" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F39" t="str">
-        <v>Оглед на обект; Контрол на доставка на материали; Подаване на документи</v>
+        <v>Контрол на доставка на материали; Среща в администрацията</v>
       </c>
       <c r="G39">
-        <v>45823</v>
+        <v>45680</v>
       </c>
       <c r="H39">
-        <v>45847</v>
+        <v>45725</v>
       </c>
       <c r="I39">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="J39">
-        <v>1.39</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="40">
@@ -1503,25 +1503,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D40" t="str">
-        <v>MONA 5, Манастирски ливади-изток; MONA 6, Манастирски ливади-изток; SONATA, ул. Филип Аврамов</v>
+        <v>MONA 5, Манастирски ливади-изток; SECRET GARDENS, Лозенец; НАП, Централно управление</v>
       </c>
       <c r="E40" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F40" t="str">
-        <v>Контрол на доставка на материали; Оглед на обект; Контрол на СМР</v>
+        <v>Среща с клиент; Контрол на СМР; Подаване на документи</v>
       </c>
       <c r="G40">
-        <v>45847</v>
+        <v>45725</v>
       </c>
       <c r="H40">
-        <v>45872</v>
+        <v>45749</v>
       </c>
       <c r="I40">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J40">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="41">
@@ -1529,31 +1529,31 @@
         <v>32</v>
       </c>
       <c r="B41" t="str">
-        <v>16.09.2026</v>
+        <v>17.09.2026</v>
       </c>
       <c r="C41" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D41" t="str">
-        <v>SONATA, ул. Филип Аврамов; SLOW LIFE, Владая; Съдебна палата, бул. Витоша 2</v>
+        <v>SREDA, Манастирски ливади-изток; Столична община, ул. Московска 33; Агенция по вписванията</v>
       </c>
       <c r="E41" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F41" t="str">
-        <v>Оглед на обект; Получаване на документи</v>
+        <v>Контрол на доставка на материали; Получаване на документи; Среща в администрацията</v>
       </c>
       <c r="G41">
-        <v>45872</v>
+        <v>45749</v>
       </c>
       <c r="H41">
-        <v>45907</v>
+        <v>45774</v>
       </c>
       <c r="I41">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="J41">
-        <v>2.03</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="42">
@@ -1561,31 +1561,31 @@
         <v>33</v>
       </c>
       <c r="B42" t="str">
-        <v>16.09.2026</v>
+        <v>17.09.2026</v>
       </c>
       <c r="C42" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D42" t="str">
-        <v>KRISTA, Кръстова вада; Столична община, ул. Московска 33; МРРБ, ул. Св. св. Кирил и Методий 17</v>
+        <v>MONA 5, Манастирски ливади-изток; MONA 6, Манастирски ливади-изток; ДНСК</v>
       </c>
       <c r="E42" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F42" t="str">
-        <v>Контрол на доставка на материали; Справка и съгласуване; Подаване на документи</v>
+        <v>Приемане на изпълнени СМР; Контрол на СМР; Получаване на документи</v>
       </c>
       <c r="G42">
-        <v>45907</v>
+        <v>45774</v>
       </c>
       <c r="H42">
-        <v>45929</v>
+        <v>45799</v>
       </c>
       <c r="I42">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J42">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="43">
@@ -1599,25 +1599,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D43" t="str">
-        <v>SONATA, ул. Филип Аврамов; НАП, Централно управление; ДНСК</v>
+        <v>Посещение при клиент</v>
       </c>
       <c r="E43" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F43" t="str">
-        <v>Среща с подизпълнител; Получаване на документи; Среща в администрацията</v>
+        <v>Консултация при клиент</v>
       </c>
       <c r="G43">
-        <v>45929</v>
+        <v>45799</v>
       </c>
       <c r="H43">
-        <v>45949</v>
+        <v>45814</v>
       </c>
       <c r="I43">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J43">
-        <v>1.16</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="44">
@@ -1625,31 +1625,31 @@
         <v>35</v>
       </c>
       <c r="B44" t="str">
-        <v>17.09.2026</v>
+        <v>18.09.2026</v>
       </c>
       <c r="C44" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D44" t="str">
-        <v>AVIVA Living, Възраждане; KRISTA, Кръстова вада; АГКК (Кадастър)</v>
+        <v>Столична община, ул. Московска 33; МРРБ, ул. Св. св. Кирил и Методий 17; АГКК (Кадастър)</v>
       </c>
       <c r="E44" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F44" t="str">
-        <v>Оглед на обект; Среща с подизпълнител; Подаване на документи</v>
+        <v>Среща в администрацията; Подаване на документи</v>
       </c>
       <c r="G44">
-        <v>45949</v>
+        <v>45814</v>
       </c>
       <c r="H44">
-        <v>45975</v>
+        <v>45835</v>
       </c>
       <c r="I44">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J44">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="45">
@@ -1657,31 +1657,31 @@
         <v>36</v>
       </c>
       <c r="B45" t="str">
-        <v>17.09.2026</v>
+        <v>18.09.2026</v>
       </c>
       <c r="C45" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D45" t="str">
-        <v>Посещение при клиент</v>
+        <v>SECRET GARDENS, Лозенец; SONATA, ул. Филип Аврамов; Агенция по вписванията</v>
       </c>
       <c r="E45" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F45" t="str">
-        <v>Среща с клиент</v>
+        <v>Контрол на СМР; Среща с клиент; Справка и съгласуване</v>
       </c>
       <c r="G45">
-        <v>45975</v>
+        <v>45835</v>
       </c>
       <c r="H45">
-        <v>45997</v>
+        <v>45856</v>
       </c>
       <c r="I45">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J45">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="46">
@@ -1695,25 +1695,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D46" t="str">
-        <v>MONA 6, Манастирски ливади-изток</v>
+        <v>KRISTA, Кръстова вада; Съдебна палата, бул. Витоша 2; ДНСК</v>
       </c>
       <c r="E46" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F46" t="str">
-        <v>Приемане на изпълнени СМР</v>
+        <v>Контрол на СМР; Подаване на документи; Среща в администрацията</v>
       </c>
       <c r="G46">
-        <v>45997</v>
+        <v>45856</v>
       </c>
       <c r="H46">
-        <v>46015</v>
+        <v>45880</v>
       </c>
       <c r="I46">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J46">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="47">
@@ -1721,31 +1721,31 @@
         <v>38</v>
       </c>
       <c r="B47" t="str">
-        <v>18.09.2026</v>
+        <v>21.09.2026</v>
       </c>
       <c r="C47" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D47" t="str">
-        <v>AVIVA Living, Възраждане; Съдебна палата, бул. Витоша 2; НАП, Централно управление</v>
+        <v>SREDA, Манастирски ливади-изток; МРРБ, ул. Св. св. Кирил и Методий 17; ДНСК</v>
       </c>
       <c r="E47" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F47" t="str">
-        <v>Среща с клиент; Подаване на документи</v>
+        <v>Контрол на СМР; Подаване на документи; Справка и съгласуване</v>
       </c>
       <c r="G47">
-        <v>46015</v>
+        <v>45880</v>
       </c>
       <c r="H47">
-        <v>46038</v>
+        <v>45904</v>
       </c>
       <c r="I47">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J47">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="48">
@@ -1759,25 +1759,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D48" t="str">
-        <v>AVIVA Living, Възраждане; НАП, Централно управление; ДНСК</v>
+        <v>SREDA, Манастирски ливади-изток; AVIVA Living, Възраждане; ДНСК</v>
       </c>
       <c r="E48" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F48" t="str">
-        <v>Контрол на доставка на материали; Среща в администрацията</v>
+        <v>Контрол на доставка на материали; Оглед на обект; Подаване на документи</v>
       </c>
       <c r="G48">
-        <v>46038</v>
+        <v>45904</v>
       </c>
       <c r="H48">
-        <v>46061</v>
+        <v>45929</v>
       </c>
       <c r="I48">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J48">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="49">
@@ -1791,25 +1791,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D49" t="str">
-        <v>Посещение при клиент</v>
+        <v>AVIVA Living, Възраждане; Столична община, ул. Московска 33; Съдебна палата, бул. Витоша 2</v>
       </c>
       <c r="E49" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F49" t="str">
-        <v>Консултация при клиент</v>
+        <v>Контрол на доставка на материали; Получаване на документи; Подаване на документи</v>
       </c>
       <c r="G49">
-        <v>46061</v>
+        <v>45929</v>
       </c>
       <c r="H49">
-        <v>46085</v>
+        <v>45950</v>
       </c>
       <c r="I49">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J49">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="50">
@@ -1823,25 +1823,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D50" t="str">
-        <v>MONA 5, Манастирски ливади-изток; UPTOWN SQUARE, Лозенец; НАП, Централно управление</v>
+        <v>SREDA, Манастирски ливади-изток; НАП, Централно управление; Агенция по вписванията</v>
       </c>
       <c r="E50" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F50" t="str">
-        <v>Контрол на СМР; Справка и съгласуване</v>
+        <v>Контрол на СМР; Подаване на документи; Среща в администрацията</v>
       </c>
       <c r="G50">
-        <v>46085</v>
+        <v>45950</v>
       </c>
       <c r="H50">
-        <v>46109</v>
+        <v>45975</v>
       </c>
       <c r="I50">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J50">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="51">
@@ -1855,25 +1855,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D51" t="str">
-        <v>МРРБ, ул. Св. св. Кирил и Методий 17; Агенция по вписванията</v>
+        <v>SONATA, ул. Филип Аврамов; AVIVA Living, Възраждане; Столична община, ул. Московска 33</v>
       </c>
       <c r="E51" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F51" t="str">
-        <v>Среща в администрацията</v>
+        <v>Среща с подизпълнител; Контрол на доставка на материали; Среща в администрацията</v>
       </c>
       <c r="G51">
-        <v>46109</v>
+        <v>45975</v>
       </c>
       <c r="H51">
-        <v>46125</v>
+        <v>45996</v>
       </c>
       <c r="I51">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J51">
-        <v>0.93</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="52">
@@ -1881,31 +1881,31 @@
         <v>43</v>
       </c>
       <c r="B52" t="str">
-        <v>24.09.2026</v>
+        <v>23.09.2026</v>
       </c>
       <c r="C52" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D52" t="str">
-        <v>MONA 5, Манастирски ливади-изток; Столична община, ул. Московска 33; Агенция по вписванията</v>
+        <v>SLOW LIFE, Владая; МРРБ, ул. Св. св. Кирил и Методий 17; ДНСК</v>
       </c>
       <c r="E52" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F52" t="str">
-        <v>Контрол на СМР; Подаване на документи; Получаване на документи</v>
+        <v>Контрол на доставка на материали; Подаване на документи; Среща в администрацията</v>
       </c>
       <c r="G52">
-        <v>46125</v>
+        <v>45996</v>
       </c>
       <c r="H52">
-        <v>46150</v>
+        <v>46041</v>
       </c>
       <c r="I52">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="J52">
-        <v>1.45</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="53">
@@ -1913,31 +1913,31 @@
         <v>44</v>
       </c>
       <c r="B53" t="str">
-        <v>24.09.2026</v>
+        <v>23.09.2026</v>
       </c>
       <c r="C53" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D53" t="str">
-        <v>Столична община, ул. Московска 33; НАП, Централно управление</v>
+        <v>Посещение при клиент</v>
       </c>
       <c r="E53" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F53" t="str">
-        <v>Получаване на документи; Подаване на документи</v>
+        <v>Консултация при клиент</v>
       </c>
       <c r="G53">
-        <v>46150</v>
+        <v>46041</v>
       </c>
       <c r="H53">
-        <v>46165</v>
+        <v>46067</v>
       </c>
       <c r="I53">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J53">
-        <v>0.87</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="54">
@@ -1951,25 +1951,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D54" t="str">
-        <v>Посещение при клиент</v>
+        <v>MONA 5, Манастирски ливади-изток; Съдебна палата, бул. Витоша 2; АГКК (Кадастър)</v>
       </c>
       <c r="E54" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F54" t="str">
-        <v>Оглед при клиент</v>
+        <v>Приемане на изпълнени СМР; Получаване на документи; Подаване на документи</v>
       </c>
       <c r="G54">
-        <v>46165</v>
+        <v>46067</v>
       </c>
       <c r="H54">
-        <v>46190</v>
+        <v>46094</v>
       </c>
       <c r="I54">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J54">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="55">
@@ -1977,31 +1977,31 @@
         <v>46</v>
       </c>
       <c r="B55" t="str">
-        <v>25.09.2026</v>
+        <v>24.09.2026</v>
       </c>
       <c r="C55" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D55" t="str">
-        <v>SREDA, Манастирски ливади-изток; SONATA, ул. Филип Аврамов; Агенция по вписванията</v>
+        <v>MONA 6, Манастирски ливади-изток; SONATA, ул. Филип Аврамов; АГКК (Кадастър)</v>
       </c>
       <c r="E55" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F55" t="str">
-        <v>Приемане на изпълнени СМР; Оглед на обект; Среща в администрацията</v>
+        <v>Приемане на изпълнени СМР; Среща с подизпълнител; Среща в администрацията</v>
       </c>
       <c r="G55">
-        <v>46190</v>
+        <v>46094</v>
       </c>
       <c r="H55">
-        <v>46215</v>
+        <v>46121</v>
       </c>
       <c r="I55">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J55">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="56">
@@ -2009,31 +2009,31 @@
         <v>47</v>
       </c>
       <c r="B56" t="str">
-        <v>25.09.2026</v>
+        <v>24.09.2026</v>
       </c>
       <c r="C56" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D56" t="str">
-        <v>Съдебна палата, бул. Витоша 2; НАП, Централно управление; ДНСК</v>
+        <v>SECRET GARDENS, Лозенец; SONATA, ул. Филип Аврамов; ДНСК</v>
       </c>
       <c r="E56" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F56" t="str">
-        <v>Получаване на документи; Среща в администрацията; Справка и съгласуване</v>
+        <v>Среща с подизпълнител; Справка и съгласуване</v>
       </c>
       <c r="G56">
-        <v>46215</v>
+        <v>46121</v>
       </c>
       <c r="H56">
-        <v>46234</v>
+        <v>46141</v>
       </c>
       <c r="I56">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J56">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="57">
@@ -2047,25 +2047,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D57" t="str">
-        <v>SREDA, Манастирски ливади-изток; KRISTA, Кръстова вада; Съдебна палата, бул. Витоша 2</v>
+        <v>SLOW LIFE, Владая; Съдебна палата, бул. Витоша 2; ДНСК</v>
       </c>
       <c r="E57" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F57" t="str">
-        <v>Среща с подизпълнител; Приемане на изпълнени СМР; Справка и съгласуване</v>
+        <v>Контрол на СМР; Получаване на документи; Подаване на документи</v>
       </c>
       <c r="G57">
-        <v>46234</v>
+        <v>46141</v>
       </c>
       <c r="H57">
-        <v>46258</v>
+        <v>46186</v>
       </c>
       <c r="I57">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="J57">
-        <v>1.39</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="58">
@@ -2073,31 +2073,31 @@
         <v>49</v>
       </c>
       <c r="B58" t="str">
-        <v>28.09.2026</v>
+        <v>25.09.2026</v>
       </c>
       <c r="C58" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D58" t="str">
-        <v>SECRET GARDENS, Лозенец; SLOW LIFE, Владая; ДНСК</v>
+        <v>MONA 6, Манастирски ливади-изток; SLOW LIFE, Владая; МРРБ, ул. Св. св. Кирил и Методий 17</v>
       </c>
       <c r="E58" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F58" t="str">
-        <v>Контрол на доставка на материали; Контрол на СМР; Подаване на документи</v>
+        <v>Приемане на изпълнени СМР; Среща с подизпълнител; Получаване на документи</v>
       </c>
       <c r="G58">
-        <v>46258</v>
+        <v>46186</v>
       </c>
       <c r="H58">
-        <v>46294</v>
+        <v>46224</v>
       </c>
       <c r="I58">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J58">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="59">
@@ -2105,31 +2105,31 @@
         <v>50</v>
       </c>
       <c r="B59" t="str">
-        <v>28.09.2026</v>
+        <v>25.09.2026</v>
       </c>
       <c r="C59" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D59" t="str">
-        <v>UPTOWN SQUARE, Лозенец; SLOW LIFE, Владая; Агенция по вписванията</v>
+        <v>SREDA, Манастирски ливади-изток; SECRET GARDENS, Лозенец; AVIVA Living, Възраждане</v>
       </c>
       <c r="E59" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F59" t="str">
-        <v>Контрол на СМР; Приемане на изпълнени СМР; Среща в администрацията</v>
+        <v>Среща с клиент; Контрол на доставка на материали; Приемане на изпълнени СМР</v>
       </c>
       <c r="G59">
-        <v>46294</v>
+        <v>46224</v>
       </c>
       <c r="H59">
-        <v>46330</v>
+        <v>46251</v>
       </c>
       <c r="I59">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="J59">
-        <v>2.09</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="60">
@@ -2137,31 +2137,31 @@
         <v>51</v>
       </c>
       <c r="B60" t="str">
-        <v>28.09.2026</v>
+        <v>25.09.2026</v>
       </c>
       <c r="C60" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D60" t="str">
-        <v>MONA 6, Манастирски ливади-изток; Столична община, ул. Московска 33; МРРБ, ул. Св. св. Кирил и Методий 17</v>
+        <v>Посещение при клиент</v>
       </c>
       <c r="E60" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F60" t="str">
-        <v>Контрол на СМР; Среща в администрацията; Подаване на документи</v>
+        <v>Оглед при клиент</v>
       </c>
       <c r="G60">
-        <v>46330</v>
+        <v>46251</v>
       </c>
       <c r="H60">
-        <v>46352</v>
+        <v>46271</v>
       </c>
       <c r="I60">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J60">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="61">
@@ -2169,31 +2169,31 @@
         <v>52</v>
       </c>
       <c r="B61" t="str">
-        <v>29.09.2026</v>
+        <v>28.09.2026</v>
       </c>
       <c r="C61" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D61" t="str">
-        <v>UPTOWN SQUARE, Лозенец; Съдебна палата, бул. Витоша 2</v>
+        <v>AVIVA Living, Възраждане; SLOW LIFE, Владая; Съдебна палата, бул. Витоша 2</v>
       </c>
       <c r="E61" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F61" t="str">
-        <v>Среща с клиент; Получаване на документи</v>
+        <v>Приемане на изпълнени СМР; Среща с клиент; Подаване на документи</v>
       </c>
       <c r="G61">
-        <v>46352</v>
+        <v>46271</v>
       </c>
       <c r="H61">
-        <v>46365</v>
+        <v>46308</v>
       </c>
       <c r="I61">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="J61">
-        <v>0.75</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="62">
@@ -2201,25 +2201,25 @@
         <v>53</v>
       </c>
       <c r="B62" t="str">
-        <v>29.09.2026</v>
+        <v>28.09.2026</v>
       </c>
       <c r="C62" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D62" t="str">
-        <v>SECRET GARDENS, Лозенец; SONATA, ул. Филип Аврамов; НАП, Централно управление</v>
+        <v>SECRET GARDENS, Лозенец; Съдебна палата, бул. Витоша 2; ДНСК</v>
       </c>
       <c r="E62" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F62" t="str">
-        <v>Контрол на СМР; Приемане на изпълнени СМР; Получаване на документи</v>
+        <v>Среща с подизпълнител; Получаване на документи; Подаване на документи</v>
       </c>
       <c r="G62">
-        <v>46365</v>
+        <v>46308</v>
       </c>
       <c r="H62">
-        <v>46385</v>
+        <v>46328</v>
       </c>
       <c r="I62">
         <v>20</v>
@@ -2233,31 +2233,31 @@
         <v>54</v>
       </c>
       <c r="B63" t="str">
-        <v>29.09.2026</v>
+        <v>28.09.2026</v>
       </c>
       <c r="C63" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D63" t="str">
-        <v>Посещение при клиент</v>
+        <v>SREDA, Манастирски ливади-изток; SONATA, ул. Филип Аврамов; SLOW LIFE, Владая</v>
       </c>
       <c r="E63" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F63" t="str">
-        <v>Среща с клиент</v>
+        <v>Контрол на доставка на материали; Среща с подизпълнител</v>
       </c>
       <c r="G63">
-        <v>46385</v>
+        <v>46328</v>
       </c>
       <c r="H63">
-        <v>46424</v>
+        <v>46377</v>
       </c>
       <c r="I63">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="J63">
-        <v>2.26</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="64">
@@ -2265,31 +2265,31 @@
         <v>55</v>
       </c>
       <c r="B64" t="str">
-        <v>30.09.2026</v>
+        <v>28.09.2026</v>
       </c>
       <c r="C64" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D64" t="str">
-        <v>SREDA, Манастирски ливади-изток; AVIVA Living, Възраждане; НАП, Централно управление</v>
+        <v>Посещение при клиент</v>
       </c>
       <c r="E64" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F64" t="str">
-        <v>Контрол на СМР; Среща с клиент; Получаване на документи</v>
+        <v>Връчване на документи на клиент</v>
       </c>
       <c r="G64">
-        <v>46424</v>
+        <v>46377</v>
       </c>
       <c r="H64">
-        <v>46449</v>
+        <v>46389</v>
       </c>
       <c r="I64">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J64">
-        <v>1.45</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="65">
@@ -2297,112 +2297,208 @@
         <v>56</v>
       </c>
       <c r="B65" t="str">
+        <v>29.09.2026</v>
+      </c>
+      <c r="C65" t="str">
+        <v>BLD – офис, ул. „Тинтява“ 126, София</v>
+      </c>
+      <c r="D65" t="str">
+        <v>SECRET GARDENS, Лозенец; AVIVA Living, Възраждане; МРРБ, ул. Св. св. Кирил и Методий 17</v>
+      </c>
+      <c r="E65" t="str">
+        <v>BLD – офис, ул. „Тинтява“ 126, София</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Контрол на доставка на материали; Приемане на изпълнени СМР; Подаване на документи</v>
+      </c>
+      <c r="G65">
+        <v>46389</v>
+      </c>
+      <c r="H65">
+        <v>46410</v>
+      </c>
+      <c r="I65">
+        <v>21</v>
+      </c>
+      <c r="J65">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>57</v>
+      </c>
+      <c r="B66" t="str">
         <v>30.09.2026</v>
       </c>
-      <c r="C65" t="str">
-        <v>BLD – офис, ул. „Тинтява“ 126, София</v>
-      </c>
-      <c r="D65" t="str">
-        <v>Посещение при клиент</v>
-      </c>
-      <c r="E65" t="str">
-        <v>BLD – офис, ул. „Тинтява“ 126, София</v>
-      </c>
-      <c r="F65" t="str">
-        <v>Среща с клиент</v>
-      </c>
-      <c r="G65">
-        <v>46449</v>
-      </c>
-      <c r="H65">
+      <c r="C66" t="str">
+        <v>BLD – офис, ул. „Тинтява“ 126, София</v>
+      </c>
+      <c r="D66" t="str">
+        <v>MONA 5, Манастирски ливади-изток; AVIVA Living, Възраждане; KRISTA, Кръстова вада</v>
+      </c>
+      <c r="E66" t="str">
+        <v>BLD – офис, ул. „Тинтява“ 126, София</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Приемане на изпълнени СМР; Оглед на обект</v>
+      </c>
+      <c r="G66">
+        <v>46410</v>
+      </c>
+      <c r="H66">
+        <v>46438</v>
+      </c>
+      <c r="I66">
+        <v>28</v>
+      </c>
+      <c r="J66">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>58</v>
+      </c>
+      <c r="B67" t="str">
+        <v>30.09.2026</v>
+      </c>
+      <c r="C67" t="str">
+        <v>BLD – офис, ул. „Тинтява“ 126, София</v>
+      </c>
+      <c r="D67" t="str">
+        <v>KRISTA, Кръстова вада; МРРБ, ул. Св. св. Кирил и Методий 17; ДНСК</v>
+      </c>
+      <c r="E67" t="str">
+        <v>BLD – офис, ул. „Тинтява“ 126, София</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Среща с клиент; Подаване на документи; Справка и съгласуване</v>
+      </c>
+      <c r="G67">
+        <v>46438</v>
+      </c>
+      <c r="H67">
+        <v>46462</v>
+      </c>
+      <c r="I67">
+        <v>24</v>
+      </c>
+      <c r="J67">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>59</v>
+      </c>
+      <c r="B68" t="str">
+        <v>30.09.2026</v>
+      </c>
+      <c r="C68" t="str">
+        <v>BLD – офис, ул. „Тинтява“ 126, София</v>
+      </c>
+      <c r="D68" t="str">
+        <v>AVIVA Living, Възраждане; МРРБ, ул. Св. св. Кирил и Методий 17</v>
+      </c>
+      <c r="E68" t="str">
+        <v>BLD – офис, ул. „Тинтява“ 126, София</v>
+      </c>
+      <c r="F68" t="str">
+        <v>Среща с подизпълнител; Справка и съгласуване</v>
+      </c>
+      <c r="G68">
+        <v>46462</v>
+      </c>
+      <c r="H68">
         <v>46480</v>
       </c>
-      <c r="I65">
-        <v>31</v>
-      </c>
-      <c r="J65">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v/>
-      </c>
-      <c r="B66" t="str">
-        <v/>
-      </c>
-      <c r="C66" t="str">
-        <v>ОБЩО за периода</v>
-      </c>
-      <c r="D66" t="str">
-        <v/>
-      </c>
-      <c r="E66" t="str">
-        <v/>
-      </c>
-      <c r="F66" t="str">
-        <v/>
-      </c>
-      <c r="G66">
-        <v>45000</v>
-      </c>
-      <c r="H66">
-        <v>46480</v>
-      </c>
-      <c r="I66">
-        <v>1480</v>
-      </c>
-      <c r="J66">
-        <v>85.82</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>Зареждания: дата</v>
-      </c>
-      <c r="B68" t="str">
-        <v>Количество, л</v>
-      </c>
-      <c r="C68" t="str">
-        <v>№ на фактура</v>
+      <c r="I68">
+        <v>18</v>
+      </c>
+      <c r="J68">
+        <v>1.04</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>08.09.2026</v>
-      </c>
-      <c r="B69">
-        <v>42.5</v>
+        <v/>
+      </c>
+      <c r="B69" t="str">
+        <v/>
       </c>
       <c r="C69" t="str">
-        <v>F-0012345</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>22.09.2026</v>
-      </c>
-      <c r="B70">
-        <v>38.1</v>
-      </c>
-      <c r="C70" t="str">
-        <v>F-0012871</v>
+        <v>ОБЩО за периода</v>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69">
+        <v>45000</v>
+      </c>
+      <c r="H69">
+        <v>46480</v>
+      </c>
+      <c r="I69">
+        <v>1480</v>
+      </c>
+      <c r="J69">
+        <v>85.84</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Зареждания: дата</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Количество, л</v>
+      </c>
+      <c r="C71" t="str">
+        <v>№ на фактура</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
+        <v>08.09.2026</v>
+      </c>
+      <c r="B72">
+        <v>42.5</v>
+      </c>
+      <c r="C72" t="str">
+        <v>F-0012345</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>22.09.2026</v>
+      </c>
+      <c r="B73">
+        <v>38.1</v>
+      </c>
+      <c r="C73" t="str">
+        <v>F-0012871</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
         <v>Водач: ____________</v>
       </c>
-      <c r="B72" t="str">
+      <c r="B75" t="str">
         <v/>
       </c>
-      <c r="C72" t="str">
-        <v>Одобрил: ____________ Димитър Бончев Савов</v>
+      <c r="C75" t="str">
+        <v>Одобрил: ____________</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J72"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J75"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/primeren-paten-list.xlsx
+++ b/primeren-paten-list.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -543,25 +543,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D10" t="str">
-        <v>MONA 5, Манастирски ливади-изток; SREDA, Манастирски ливади-изток; SLOW LIFE, Владая</v>
+        <v>SECRET GARDENS, Лозенец; KRISTA, Кръстова вада; НАП, Централно управление</v>
       </c>
       <c r="E10" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F10" t="str">
-        <v>Среща с клиент; Приемане на изпълнени СМР; Среща с подизпълнител</v>
+        <v>Контрол на доставка на материали; Контрол на СМР; Среща в администрацията</v>
       </c>
       <c r="G10">
         <v>45000</v>
       </c>
       <c r="H10">
-        <v>45049</v>
+        <v>45022</v>
       </c>
       <c r="I10">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="J10">
-        <v>2.84</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="11">
@@ -575,25 +575,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D11" t="str">
-        <v>SECRET GARDENS, Лозенец; Столична община, ул. Московска 33; АГКК (Кадастър)</v>
+        <v>AVIVA Living, Възраждане; SLOW LIFE, Владая; Съдебна палата, бул. Витоша 2</v>
       </c>
       <c r="E11" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F11" t="str">
-        <v>Среща с клиент; Справка и съгласуване</v>
+        <v>Среща с подизпълнител; Приемане на изпълнени СМР; Получаване на документи</v>
       </c>
       <c r="G11">
-        <v>45049</v>
+        <v>45022</v>
       </c>
       <c r="H11">
-        <v>45072</v>
+        <v>45059</v>
       </c>
       <c r="I11">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J11">
-        <v>1.33</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="12">
@@ -601,31 +601,31 @@
         <v>3</v>
       </c>
       <c r="B12" t="str">
-        <v>01.09.2026</v>
+        <v>02.09.2026</v>
       </c>
       <c r="C12" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D12" t="str">
-        <v>Посещение при клиент</v>
+        <v>UPTOWN SQUARE, Лозенец; Агенция по вписванията; АГКК (Кадастър)</v>
       </c>
       <c r="E12" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F12" t="str">
-        <v>Оглед при клиент</v>
+        <v>Контрол на доставка на материали; Получаване на документи</v>
       </c>
       <c r="G12">
-        <v>45072</v>
+        <v>45059</v>
       </c>
       <c r="H12">
-        <v>45088</v>
+        <v>45081</v>
       </c>
       <c r="I12">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J12">
-        <v>0.93</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="13">
@@ -639,25 +639,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D13" t="str">
-        <v>Столична община, ул. Московска 33; МРРБ, ул. Св. св. Кирил и Методий 17; Съдебна палата, бул. Витоша 2</v>
+        <v>SLOW LIFE, Владая; НАП, Централно управление; Агенция по вписванията</v>
       </c>
       <c r="E13" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F13" t="str">
-        <v>Подаване на документи; Получаване на документи; Справка и съгласуване</v>
+        <v>Оглед на обект; Справка и съгласуване</v>
       </c>
       <c r="G13">
-        <v>45088</v>
+        <v>45081</v>
       </c>
       <c r="H13">
-        <v>45104</v>
+        <v>45127</v>
       </c>
       <c r="I13">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="J13">
-        <v>0.93</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="14">
@@ -671,25 +671,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D14" t="str">
-        <v>SREDA, Манастирски ливади-изток; AVIVA Living, Възраждане; ДНСК</v>
+        <v>SECRET GARDENS, Лозенец; SONATA, ул. Филип Аврамов; МРРБ, ул. Св. св. Кирил и Методий 17</v>
       </c>
       <c r="E14" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F14" t="str">
-        <v>Среща с подизпълнител; Приемане на изпълнени СМР; Справка и съгласуване</v>
+        <v>Приемане на изпълнени СМР; Оглед на обект; Получаване на документи</v>
       </c>
       <c r="G14">
-        <v>45104</v>
+        <v>45127</v>
       </c>
       <c r="H14">
-        <v>45129</v>
+        <v>45146</v>
       </c>
       <c r="I14">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J14">
-        <v>1.45</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="15">
@@ -709,19 +709,19 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F15" t="str">
-        <v>Консултация при клиент</v>
+        <v>Връчване на документи на клиент</v>
       </c>
       <c r="G15">
-        <v>45129</v>
+        <v>45146</v>
       </c>
       <c r="H15">
-        <v>45172</v>
+        <v>45175</v>
       </c>
       <c r="I15">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="J15">
-        <v>2.49</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="16">
@@ -735,25 +735,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D16" t="str">
-        <v>MONA 5, Манастирски ливади-изток; АГКК (Кадастър); ДНСК</v>
+        <v>SECRET GARDENS, Лозенец; SONATA, ул. Филип Аврамов; МРРБ, ул. Св. св. Кирил и Методий 17</v>
       </c>
       <c r="E16" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F16" t="str">
-        <v>Среща с подизпълнител; Получаване на документи; Справка и съгласуване</v>
+        <v>Контрол на СМР; Оглед на обект; Получаване на документи</v>
       </c>
       <c r="G16">
-        <v>45172</v>
+        <v>45175</v>
       </c>
       <c r="H16">
-        <v>45197</v>
+        <v>45194</v>
       </c>
       <c r="I16">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J16">
-        <v>1.45</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="17">
@@ -767,25 +767,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D17" t="str">
-        <v>MONA 5, Манастирски ливади-изток; UPTOWN SQUARE, Лозенец; AVIVA Living, Възраждане</v>
+        <v>SECRET GARDENS, Лозенец; AVIVA Living, Възраждане; ДНСК</v>
       </c>
       <c r="E17" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F17" t="str">
-        <v>Контрол на СМР; Контрол на доставка на материали; Приемане на изпълнени СМР</v>
+        <v>Среща с подизпълнител; Оглед на обект; Справка и съгласуване</v>
       </c>
       <c r="G17">
-        <v>45197</v>
+        <v>45194</v>
       </c>
       <c r="H17">
-        <v>45224</v>
+        <v>45216</v>
       </c>
       <c r="I17">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J17">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="18">
@@ -799,25 +799,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D18" t="str">
-        <v>МРРБ, ул. Св. св. Кирил и Методий 17; Съдебна палата, бул. Витоша 2; Агенция по вписванията</v>
+        <v>MONA 6, Манастирски ливади-изток; SONATA, ул. Филип Аврамов; Столична община, ул. Московска 33</v>
       </c>
       <c r="E18" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F18" t="str">
-        <v>Подаване на документи; Справка и съгласуване; Среща в администрацията</v>
+        <v>Среща с подизпълнител; Среща с клиент; Справка и съгласуване</v>
       </c>
       <c r="G18">
-        <v>45224</v>
+        <v>45216</v>
       </c>
       <c r="H18">
-        <v>45243</v>
+        <v>45239</v>
       </c>
       <c r="I18">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J18">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="19">
@@ -825,31 +825,31 @@
         <v>10</v>
       </c>
       <c r="B19" t="str">
-        <v>04.09.2026</v>
+        <v>03.09.2026</v>
       </c>
       <c r="C19" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D19" t="str">
-        <v>SONATA, ул. Филип Аврамов; SLOW LIFE, Владая; АГКК (Кадастър)</v>
+        <v>Посещение при клиент</v>
       </c>
       <c r="E19" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F19" t="str">
-        <v>Среща с подизпълнител; Контрол на СМР; Получаване на документи</v>
+        <v>Оглед при клиент</v>
       </c>
       <c r="G19">
-        <v>45243</v>
+        <v>45239</v>
       </c>
       <c r="H19">
-        <v>45281</v>
+        <v>45255</v>
       </c>
       <c r="I19">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="J19">
-        <v>2.2</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="20">
@@ -863,25 +863,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D20" t="str">
-        <v>SECRET GARDENS, Лозенец; AVIVA Living, Възраждане; Столична община, ул. Московска 33</v>
+        <v>SLOW LIFE, Владая; МРРБ, ул. Св. св. Кирил и Методий 17; НАП, Централно управление</v>
       </c>
       <c r="E20" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F20" t="str">
-        <v>Контрол на доставка на материали; Среща в администрацията</v>
+        <v>Контрол на СМР; Подаване на документи; Получаване на документи</v>
       </c>
       <c r="G20">
-        <v>45281</v>
+        <v>45255</v>
       </c>
       <c r="H20">
-        <v>45302</v>
+        <v>45300</v>
       </c>
       <c r="I20">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="J20">
-        <v>1.22</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="21">
@@ -895,25 +895,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D21" t="str">
-        <v>Столична община, ул. Московска 33; Агенция по вписванията</v>
+        <v>SLOW LIFE, Владая; МРРБ, ул. Св. св. Кирил и Методий 17; Агенция по вписванията</v>
       </c>
       <c r="E21" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F21" t="str">
-        <v>Получаване на документи; Справка и съгласуване</v>
+        <v>Приемане на изпълнени СМР; Справка и съгласуване</v>
       </c>
       <c r="G21">
-        <v>45302</v>
+        <v>45300</v>
       </c>
       <c r="H21">
-        <v>45318</v>
+        <v>45346</v>
       </c>
       <c r="I21">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="J21">
-        <v>0.93</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="22">
@@ -927,25 +927,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D22" t="str">
-        <v>MONA 5, Манастирски ливади-изток; SLOW LIFE, Владая; АГКК (Кадастър)</v>
+        <v>MONA 5, Манастирски ливади-изток; MONA 6, Манастирски ливади-изток; KRISTA, Кръстова вада</v>
       </c>
       <c r="E22" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F22" t="str">
-        <v>Контрол на СМР; Оглед на обект; Подаване на документи</v>
+        <v>Оглед на обект; Среща с подизпълнител</v>
       </c>
       <c r="G22">
-        <v>45318</v>
+        <v>45346</v>
       </c>
       <c r="H22">
-        <v>45359</v>
+        <v>45374</v>
       </c>
       <c r="I22">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="J22">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="23">
@@ -959,25 +959,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D23" t="str">
-        <v>Посещение при клиент</v>
+        <v>MONA 5, Манастирски ливади-изток; SECRET GARDENS, Лозенец; МРРБ, ул. Св. св. Кирил и Методий 17</v>
       </c>
       <c r="E23" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F23" t="str">
-        <v>Среща с клиент</v>
+        <v>Контрол на доставка на материали; Оглед на обект; Справка и съгласуване</v>
       </c>
       <c r="G23">
-        <v>45359</v>
+        <v>45374</v>
       </c>
       <c r="H23">
-        <v>45400</v>
+        <v>45397</v>
       </c>
       <c r="I23">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="J23">
-        <v>2.38</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="24">
@@ -985,31 +985,31 @@
         <v>15</v>
       </c>
       <c r="B24" t="str">
-        <v>08.09.2026</v>
+        <v>07.09.2026</v>
       </c>
       <c r="C24" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D24" t="str">
-        <v>MONA 5, Манастирски ливади-изток; MONA 6, Манастирски ливади-изток; SREDA, Манастирски ливади-изток</v>
+        <v>Посещение при клиент</v>
       </c>
       <c r="E24" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F24" t="str">
-        <v>Оглед на обект</v>
+        <v>Оглед при клиент</v>
       </c>
       <c r="G24">
-        <v>45400</v>
+        <v>45397</v>
       </c>
       <c r="H24">
-        <v>45428</v>
+        <v>45441</v>
       </c>
       <c r="I24">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="J24">
-        <v>1.62</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="25">
@@ -1023,25 +1023,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D25" t="str">
-        <v>MONA 6, Манастирски ливади-изток; AVIVA Living, Възраждане; ДНСК</v>
+        <v>MONA 6, Манастирски ливади-изток; KRISTA, Кръстова вада; АГКК (Кадастър)</v>
       </c>
       <c r="E25" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F25" t="str">
-        <v>Среща с подизпълнител; Приемане на изпълнени СМР; Получаване на документи</v>
+        <v>Оглед на обект; Среща с клиент; Подаване на документи</v>
       </c>
       <c r="G25">
-        <v>45428</v>
+        <v>45441</v>
       </c>
       <c r="H25">
-        <v>45453</v>
+        <v>45468</v>
       </c>
       <c r="I25">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J25">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="26">
@@ -1049,31 +1049,31 @@
         <v>17</v>
       </c>
       <c r="B26" t="str">
-        <v>08.09.2026</v>
+        <v>09.09.2026</v>
       </c>
       <c r="C26" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D26" t="str">
-        <v>MONA 6, Манастирски ливади-изток; UPTOWN SQUARE, Лозенец; AVIVA Living, Възраждане</v>
+        <v>MONA 6, Манастирски ливади-изток; AVIVA Living, Възраждане; МРРБ, ул. Св. св. Кирил и Методий 17</v>
       </c>
       <c r="E26" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F26" t="str">
-        <v>Среща с клиент; Оглед на обект; Приемане на изпълнени СМР</v>
+        <v>Оглед на обект; Контрол на доставка на материали; Справка и съгласуване</v>
       </c>
       <c r="G26">
-        <v>45453</v>
+        <v>45468</v>
       </c>
       <c r="H26">
-        <v>45480</v>
+        <v>45492</v>
       </c>
       <c r="I26">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J26">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="27">
@@ -1081,31 +1081,31 @@
         <v>18</v>
       </c>
       <c r="B27" t="str">
-        <v>08.09.2026</v>
+        <v>09.09.2026</v>
       </c>
       <c r="C27" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D27" t="str">
-        <v>Посещение при клиент</v>
+        <v>МРРБ, ул. Св. св. Кирил и Методий 17; Агенция по вписванията; ДНСК</v>
       </c>
       <c r="E27" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F27" t="str">
-        <v>Среща с клиент</v>
+        <v>Подаване на документи; Получаване на документи</v>
       </c>
       <c r="G27">
-        <v>45480</v>
+        <v>45492</v>
       </c>
       <c r="H27">
-        <v>45505</v>
+        <v>45511</v>
       </c>
       <c r="I27">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J27">
-        <v>1.45</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="28">
@@ -1119,25 +1119,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D28" t="str">
-        <v>SONATA, ул. Филип Аврамов; AVIVA Living, Възраждане; Съдебна палата, бул. Витоша 2</v>
+        <v>UPTOWN SQUARE, Лозенец; SLOW LIFE, Владая; Агенция по вписванията</v>
       </c>
       <c r="E28" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F28" t="str">
-        <v>Оглед на обект; Среща с подизпълнител; Справка и съгласуване</v>
+        <v>Контрол на доставка на материали; Среща с клиент; Среща в администрацията</v>
       </c>
       <c r="G28">
-        <v>45505</v>
+        <v>45511</v>
       </c>
       <c r="H28">
-        <v>45526</v>
+        <v>45547</v>
       </c>
       <c r="I28">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J28">
-        <v>1.22</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="29">
@@ -1151,25 +1151,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D29" t="str">
-        <v>SREDA, Манастирски ливади-изток; UPTOWN SQUARE, Лозенец; SLOW LIFE, Владая</v>
+        <v>Посещение при клиент</v>
       </c>
       <c r="E29" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F29" t="str">
-        <v>Среща с клиент; Контрол на СМР; Оглед на обект</v>
+        <v>Консултация при клиент</v>
       </c>
       <c r="G29">
-        <v>45526</v>
+        <v>45547</v>
       </c>
       <c r="H29">
-        <v>45575</v>
+        <v>45561</v>
       </c>
       <c r="I29">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="J29">
-        <v>2.84</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="30">
@@ -1177,31 +1177,31 @@
         <v>21</v>
       </c>
       <c r="B30" t="str">
-        <v>09.09.2026</v>
+        <v>10.09.2026</v>
       </c>
       <c r="C30" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D30" t="str">
-        <v>MONA 6, Манастирски ливади-изток; SONATA, ул. Филип Аврамов; НАП, Централно управление</v>
+        <v>MONA 6, Манастирски ливади-изток; KRISTA, Кръстова вада; Агенция по вписванията</v>
       </c>
       <c r="E30" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F30" t="str">
-        <v>Контрол на СМР; Среща с подизпълнител; Получаване на документи</v>
+        <v>Оглед на обект; Подаване на документи</v>
       </c>
       <c r="G30">
-        <v>45575</v>
+        <v>45561</v>
       </c>
       <c r="H30">
-        <v>45599</v>
+        <v>45587</v>
       </c>
       <c r="I30">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J30">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="31">
@@ -1215,7 +1215,7 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D31" t="str">
-        <v>MONA 5, Манастирски ливади-изток; MONA 6, Манастирски ливади-изток; SLOW LIFE, Владая</v>
+        <v>Посещение при клиент</v>
       </c>
       <c r="E31" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
@@ -1224,16 +1224,16 @@
         <v>Среща с клиент</v>
       </c>
       <c r="G31">
-        <v>45599</v>
+        <v>45587</v>
       </c>
       <c r="H31">
-        <v>45648</v>
+        <v>45606</v>
       </c>
       <c r="I31">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="J31">
-        <v>2.84</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="32">
@@ -1241,31 +1241,31 @@
         <v>23</v>
       </c>
       <c r="B32" t="str">
-        <v>10.09.2026</v>
+        <v>11.09.2026</v>
       </c>
       <c r="C32" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D32" t="str">
-        <v>SLOW LIFE, Владая; АГКК (Кадастър)</v>
+        <v>SONATA, ул. Филип Аврамов; SLOW LIFE, Владая; МРРБ, ул. Св. св. Кирил и Методий 17</v>
       </c>
       <c r="E32" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F32" t="str">
-        <v>Оглед на обект; Подаване на документи</v>
+        <v>Контрол на СМР; Приемане на изпълнени СМР; Получаване на документи</v>
       </c>
       <c r="G32">
-        <v>45648</v>
+        <v>45606</v>
       </c>
       <c r="H32">
-        <v>45691</v>
+        <v>45641</v>
       </c>
       <c r="I32">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J32">
-        <v>2.49</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="33">
@@ -1279,25 +1279,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D33" t="str">
-        <v>MONA 6, Манастирски ливади-изток; Столична община, ул. Московска 33; Агенция по вписванията</v>
+        <v>SREDA, Манастирски ливади-изток; SECRET GARDENS, Лозенец; ДНСК</v>
       </c>
       <c r="E33" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F33" t="str">
-        <v>Приемане на изпълнени СМР; Справка и съгласуване; Получаване на документи</v>
+        <v>Приемане на изпълнени СМР; Среща с клиент; Подаване на документи</v>
       </c>
       <c r="G33">
-        <v>45691</v>
+        <v>45641</v>
       </c>
       <c r="H33">
-        <v>45716</v>
+        <v>45665</v>
       </c>
       <c r="I33">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J33">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="34">
@@ -1305,31 +1305,31 @@
         <v>25</v>
       </c>
       <c r="B34" t="str">
-        <v>11.09.2026</v>
+        <v>14.09.2026</v>
       </c>
       <c r="C34" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D34" t="str">
-        <v>Посещение при клиент</v>
+        <v>UPTOWN SQUARE, Лозенец; МРРБ, ул. Св. св. Кирил и Методий 17; НАП, Централно управление</v>
       </c>
       <c r="E34" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F34" t="str">
-        <v>Консултация при клиент</v>
+        <v>Контрол на СМР; Среща в администрацията; Подаване на документи</v>
       </c>
       <c r="G34">
-        <v>45716</v>
+        <v>45665</v>
       </c>
       <c r="H34">
-        <v>45731</v>
+        <v>45683</v>
       </c>
       <c r="I34">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J34">
-        <v>0.87</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="35">
@@ -1343,25 +1343,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D35" t="str">
-        <v>UPTOWN SQUARE, Лозенец; SECRET GARDENS, Лозенец; Съдебна палата, бул. Витоша 2</v>
+        <v>UPTOWN SQUARE, Лозенец; SECRET GARDENS, Лозенец; АГКК (Кадастър)</v>
       </c>
       <c r="E35" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F35" t="str">
-        <v>Среща с подизпълнител; Получаване на документи</v>
+        <v>Среща с подизпълнител; Приемане на изпълнени СМР; Справка и съгласуване</v>
       </c>
       <c r="G35">
-        <v>45731</v>
+        <v>45683</v>
       </c>
       <c r="H35">
-        <v>45749</v>
+        <v>45705</v>
       </c>
       <c r="I35">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J35">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="36">
@@ -1369,31 +1369,31 @@
         <v>27</v>
       </c>
       <c r="B36" t="str">
-        <v>14.09.2026</v>
+        <v>15.09.2026</v>
       </c>
       <c r="C36" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D36" t="str">
-        <v>UPTOWN SQUARE, Лозенец; МРРБ, ул. Св. св. Кирил и Методий 17; НАП, Централно управление</v>
+        <v>AVIVA Living, Възраждане; МРРБ, ул. Св. св. Кирил и Методий 17; Агенция по вписванията</v>
       </c>
       <c r="E36" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F36" t="str">
-        <v>Контрол на СМР; Среща в администрацията; Справка и съгласуване</v>
+        <v>Контрол на доставка на материали; Среща в администрацията; Справка и съгласуване</v>
       </c>
       <c r="G36">
-        <v>45749</v>
+        <v>45705</v>
       </c>
       <c r="H36">
-        <v>45767</v>
+        <v>45729</v>
       </c>
       <c r="I36">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J36">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="37">
@@ -1401,31 +1401,31 @@
         <v>28</v>
       </c>
       <c r="B37" t="str">
-        <v>14.09.2026</v>
+        <v>15.09.2026</v>
       </c>
       <c r="C37" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D37" t="str">
-        <v>Посещение при клиент</v>
+        <v>SECRET GARDENS, Лозенец; AVIVA Living, Възраждане; SLOW LIFE, Владая</v>
       </c>
       <c r="E37" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F37" t="str">
-        <v>Среща с клиент</v>
+        <v>Приемане на изпълнени СМР; Оглед на обект</v>
       </c>
       <c r="G37">
-        <v>45767</v>
+        <v>45729</v>
       </c>
       <c r="H37">
-        <v>45784</v>
+        <v>45775</v>
       </c>
       <c r="I37">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="J37">
-        <v>0.99</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="38">
@@ -1439,25 +1439,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D38" t="str">
-        <v>SREDA, Манастирски ливади-изток; SLOW LIFE, Владая; НАП, Централно управление</v>
+        <v>MONA 5, Манастирски ливади-изток; KRISTA, Кръстова вада; Столична община, ул. Московска 33</v>
       </c>
       <c r="E38" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F38" t="str">
-        <v>Контрол на доставка на материали; Среща с клиент; Получаване на документи</v>
+        <v>Контрол на СМР; Оглед на обект; Справка и съгласуване</v>
       </c>
       <c r="G38">
-        <v>45784</v>
+        <v>45775</v>
       </c>
       <c r="H38">
-        <v>45823</v>
+        <v>45799</v>
       </c>
       <c r="I38">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="J38">
-        <v>2.26</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="39">
@@ -1471,25 +1471,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D39" t="str">
-        <v>MONA 6, Манастирски ливади-изток; KRISTA, Кръстова вада; Съдебна палата, бул. Витоша 2</v>
+        <v>Посещение при клиент</v>
       </c>
       <c r="E39" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F39" t="str">
-        <v>Оглед на обект; Контрол на доставка на материали; Подаване на документи</v>
+        <v>Среща с клиент</v>
       </c>
       <c r="G39">
-        <v>45823</v>
+        <v>45799</v>
       </c>
       <c r="H39">
-        <v>45847</v>
+        <v>45841</v>
       </c>
       <c r="I39">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="J39">
-        <v>1.39</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="40">
@@ -1503,25 +1503,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D40" t="str">
-        <v>MONA 5, Манастирски ливади-изток; MONA 6, Манастирски ливади-изток; SONATA, ул. Филип Аврамов</v>
+        <v>UPTOWN SQUARE, Лозенец; Столична община, ул. Московска 33; Агенция по вписванията</v>
       </c>
       <c r="E40" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F40" t="str">
-        <v>Контрол на доставка на материали; Оглед на обект; Контрол на СМР</v>
+        <v>Среща с клиент; Получаване на документи; Справка и съгласуване</v>
       </c>
       <c r="G40">
-        <v>45847</v>
+        <v>45841</v>
       </c>
       <c r="H40">
-        <v>45872</v>
+        <v>45860</v>
       </c>
       <c r="I40">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J40">
-        <v>1.45</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="41">
@@ -1535,25 +1535,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D41" t="str">
-        <v>SONATA, ул. Филип Аврамов; SLOW LIFE, Владая; Съдебна палата, бул. Витоша 2</v>
+        <v>SECRET GARDENS, Лозенец; AVIVA Living, Възраждане</v>
       </c>
       <c r="E41" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F41" t="str">
-        <v>Оглед на обект; Получаване на документи</v>
+        <v>Оглед на обект; Приемане на изпълнени СМР</v>
       </c>
       <c r="G41">
-        <v>45872</v>
+        <v>45860</v>
       </c>
       <c r="H41">
-        <v>45907</v>
+        <v>45879</v>
       </c>
       <c r="I41">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="J41">
-        <v>2.03</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="42">
@@ -1567,25 +1567,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D42" t="str">
-        <v>KRISTA, Кръстова вада; Столична община, ул. Московска 33; МРРБ, ул. Св. св. Кирил и Методий 17</v>
+        <v>KRISTA, Кръстова вада; Агенция по вписванията; ДНСК</v>
       </c>
       <c r="E42" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F42" t="str">
-        <v>Контрол на доставка на материали; Справка и съгласуване; Подаване на документи</v>
+        <v>Приемане на изпълнени СМР; Получаване на документи; Среща в администрацията</v>
       </c>
       <c r="G42">
-        <v>45907</v>
+        <v>45879</v>
       </c>
       <c r="H42">
-        <v>45929</v>
+        <v>45903</v>
       </c>
       <c r="I42">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J42">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="43">
@@ -1599,25 +1599,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D43" t="str">
-        <v>SONATA, ул. Филип Аврамов; НАП, Централно управление; ДНСК</v>
+        <v>MONA 6, Манастирски ливади-изток; НАП, Централно управление; Агенция по вписванията</v>
       </c>
       <c r="E43" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F43" t="str">
-        <v>Среща с подизпълнител; Получаване на документи; Среща в администрацията</v>
+        <v>Среща с подизпълнител; Получаване на документи; Подаване на документи</v>
       </c>
       <c r="G43">
-        <v>45929</v>
+        <v>45903</v>
       </c>
       <c r="H43">
-        <v>45949</v>
+        <v>45928</v>
       </c>
       <c r="I43">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J43">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="44">
@@ -1631,25 +1631,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D44" t="str">
-        <v>AVIVA Living, Възраждане; KRISTA, Кръстова вада; АГКК (Кадастър)</v>
+        <v>SREDA, Манастирски ливади-изток; SONATA, ул. Филип Аврамов; AVIVA Living, Възраждане</v>
       </c>
       <c r="E44" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F44" t="str">
-        <v>Оглед на обект; Среща с подизпълнител; Подаване на документи</v>
+        <v>Приемане на изпълнени СМР; Оглед на обект; Среща с клиент</v>
       </c>
       <c r="G44">
-        <v>45949</v>
+        <v>45928</v>
       </c>
       <c r="H44">
-        <v>45975</v>
+        <v>45955</v>
       </c>
       <c r="I44">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J44">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="45">
@@ -1669,19 +1669,19 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F45" t="str">
-        <v>Среща с клиент</v>
+        <v>Консултация при клиент</v>
       </c>
       <c r="G45">
-        <v>45975</v>
+        <v>45955</v>
       </c>
       <c r="H45">
-        <v>45997</v>
+        <v>45984</v>
       </c>
       <c r="I45">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J45">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="46">
@@ -1695,25 +1695,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D46" t="str">
-        <v>MONA 6, Манастирски ливади-изток</v>
+        <v>SECRET GARDENS, Лозенец; KRISTA, Кръстова вада; НАП, Централно управление</v>
       </c>
       <c r="E46" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F46" t="str">
-        <v>Приемане на изпълнени СМР</v>
+        <v>Среща с подизпълнител; Среща с клиент; Получаване на документи</v>
       </c>
       <c r="G46">
-        <v>45997</v>
+        <v>45984</v>
       </c>
       <c r="H46">
-        <v>46015</v>
+        <v>46006</v>
       </c>
       <c r="I46">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J46">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="47">
@@ -1727,25 +1727,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D47" t="str">
-        <v>AVIVA Living, Възраждане; Съдебна палата, бул. Витоша 2; НАП, Централно управление</v>
+        <v>UPTOWN SQUARE, Лозенец; KRISTA, Кръстова вада; НАП, Централно управление</v>
       </c>
       <c r="E47" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F47" t="str">
-        <v>Среща с клиент; Подаване на документи</v>
+        <v>Среща с подизпълнител; Контрол на СМР; Получаване на документи</v>
       </c>
       <c r="G47">
-        <v>46015</v>
+        <v>46006</v>
       </c>
       <c r="H47">
-        <v>46038</v>
+        <v>46027</v>
       </c>
       <c r="I47">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J47">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="48">
@@ -1753,31 +1753,31 @@
         <v>39</v>
       </c>
       <c r="B48" t="str">
-        <v>21.09.2026</v>
+        <v>18.09.2026</v>
       </c>
       <c r="C48" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D48" t="str">
-        <v>AVIVA Living, Възраждане; НАП, Централно управление; ДНСК</v>
+        <v>MONA 5, Манастирски ливади-изток; KRISTA, Кръстова вада; НАП, Централно управление</v>
       </c>
       <c r="E48" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F48" t="str">
-        <v>Контрол на доставка на материали; Среща в администрацията</v>
+        <v>Приемане на изпълнени СМР; Среща с клиент; Подаване на документи</v>
       </c>
       <c r="G48">
-        <v>46038</v>
+        <v>46027</v>
       </c>
       <c r="H48">
-        <v>46061</v>
+        <v>46052</v>
       </c>
       <c r="I48">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J48">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="49">
@@ -1791,25 +1791,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D49" t="str">
-        <v>Посещение при клиент</v>
+        <v>UPTOWN SQUARE, Лозенец; МРРБ, ул. Св. св. Кирил и Методий 17; НАП, Централно управление</v>
       </c>
       <c r="E49" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F49" t="str">
-        <v>Консултация при клиент</v>
+        <v>Приемане на изпълнени СМР; Подаване на документи</v>
       </c>
       <c r="G49">
-        <v>46061</v>
+        <v>46052</v>
       </c>
       <c r="H49">
-        <v>46085</v>
+        <v>46070</v>
       </c>
       <c r="I49">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J49">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="50">
@@ -1823,25 +1823,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D50" t="str">
-        <v>MONA 5, Манастирски ливади-изток; UPTOWN SQUARE, Лозенец; НАП, Централно управление</v>
+        <v>Столична община, ул. Московска 33; Съдебна палата, бул. Витоша 2</v>
       </c>
       <c r="E50" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F50" t="str">
-        <v>Контрол на СМР; Справка и съгласуване</v>
+        <v>Справка и съгласуване; Среща в администрацията</v>
       </c>
       <c r="G50">
-        <v>46085</v>
+        <v>46070</v>
       </c>
       <c r="H50">
-        <v>46109</v>
+        <v>46083</v>
       </c>
       <c r="I50">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="J50">
-        <v>1.39</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="51">
@@ -1855,25 +1855,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D51" t="str">
-        <v>МРРБ, ул. Св. св. Кирил и Методий 17; Агенция по вписванията</v>
+        <v>SECRET GARDENS, Лозенец; Съдебна палата, бул. Витоша 2; Агенция по вписванията</v>
       </c>
       <c r="E51" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F51" t="str">
-        <v>Среща в администрацията</v>
+        <v>Среща с клиент; Справка и съгласуване; Получаване на документи</v>
       </c>
       <c r="G51">
-        <v>46109</v>
+        <v>46083</v>
       </c>
       <c r="H51">
-        <v>46125</v>
+        <v>46104</v>
       </c>
       <c r="I51">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J51">
-        <v>0.93</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="52">
@@ -1881,31 +1881,31 @@
         <v>43</v>
       </c>
       <c r="B52" t="str">
-        <v>24.09.2026</v>
+        <v>23.09.2026</v>
       </c>
       <c r="C52" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D52" t="str">
-        <v>MONA 5, Манастирски ливади-изток; Столична община, ул. Московска 33; Агенция по вписванията</v>
+        <v>SECRET GARDENS, Лозенец; SLOW LIFE, Владая; Агенция по вписванията</v>
       </c>
       <c r="E52" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F52" t="str">
-        <v>Контрол на СМР; Подаване на документи; Получаване на документи</v>
+        <v>Приемане на изпълнени СМР; Оглед на обект; Среща в администрацията</v>
       </c>
       <c r="G52">
-        <v>46125</v>
+        <v>46104</v>
       </c>
       <c r="H52">
-        <v>46150</v>
+        <v>46141</v>
       </c>
       <c r="I52">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="J52">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="53">
@@ -1919,25 +1919,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D53" t="str">
-        <v>Столична община, ул. Московска 33; НАП, Централно управление</v>
+        <v>MONA 5, Манастирски ливади-изток; SREDA, Манастирски ливади-изток; МРРБ, ул. Св. св. Кирил и Методий 17</v>
       </c>
       <c r="E53" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F53" t="str">
-        <v>Получаване на документи; Подаване на документи</v>
+        <v>Контрол на СМР; Оглед на обект; Получаване на документи</v>
       </c>
       <c r="G53">
-        <v>46150</v>
+        <v>46141</v>
       </c>
       <c r="H53">
         <v>46165</v>
       </c>
       <c r="I53">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J53">
-        <v>0.87</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="54">
@@ -1951,25 +1951,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D54" t="str">
-        <v>Посещение при клиент</v>
+        <v>SECRET GARDENS, Лозенец; AVIVA Living, Възраждане; ДНСК</v>
       </c>
       <c r="E54" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F54" t="str">
-        <v>Оглед при клиент</v>
+        <v>Контрол на СМР; Получаване на документи</v>
       </c>
       <c r="G54">
         <v>46165</v>
       </c>
       <c r="H54">
-        <v>46190</v>
+        <v>46187</v>
       </c>
       <c r="I54">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J54">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="55">
@@ -1977,31 +1977,31 @@
         <v>46</v>
       </c>
       <c r="B55" t="str">
-        <v>25.09.2026</v>
+        <v>24.09.2026</v>
       </c>
       <c r="C55" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D55" t="str">
-        <v>SREDA, Манастирски ливади-изток; SONATA, ул. Филип Аврамов; Агенция по вписванията</v>
+        <v>UPTOWN SQUARE, Лозенец; SONATA, ул. Филип Аврамов</v>
       </c>
       <c r="E55" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F55" t="str">
-        <v>Приемане на изпълнени СМР; Оглед на обект; Среща в администрацията</v>
+        <v>Среща с клиент; Контрол на СМР</v>
       </c>
       <c r="G55">
-        <v>46190</v>
+        <v>46187</v>
       </c>
       <c r="H55">
-        <v>46215</v>
+        <v>46202</v>
       </c>
       <c r="I55">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J55">
-        <v>1.45</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="56">
@@ -2009,31 +2009,31 @@
         <v>47</v>
       </c>
       <c r="B56" t="str">
-        <v>25.09.2026</v>
+        <v>24.09.2026</v>
       </c>
       <c r="C56" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D56" t="str">
-        <v>Съдебна палата, бул. Витоша 2; НАП, Централно управление; ДНСК</v>
+        <v>Посещение при клиент</v>
       </c>
       <c r="E56" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F56" t="str">
-        <v>Получаване на документи; Среща в администрацията; Справка и съгласуване</v>
+        <v>Консултация при клиент</v>
       </c>
       <c r="G56">
-        <v>46215</v>
+        <v>46202</v>
       </c>
       <c r="H56">
-        <v>46234</v>
+        <v>46229</v>
       </c>
       <c r="I56">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J56">
-        <v>1.1</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="57">
@@ -2047,25 +2047,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D57" t="str">
-        <v>SREDA, Манастирски ливади-изток; KRISTA, Кръстова вада; Съдебна палата, бул. Витоша 2</v>
+        <v>SONATA, ул. Филип Аврамов; Агенция по вписванията; АГКК (Кадастър)</v>
       </c>
       <c r="E57" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F57" t="str">
-        <v>Среща с подизпълнител; Приемане на изпълнени СМР; Справка и съгласуване</v>
+        <v>Среща с подизпълнител; Получаване на документи; Подаване на документи</v>
       </c>
       <c r="G57">
-        <v>46234</v>
+        <v>46229</v>
       </c>
       <c r="H57">
-        <v>46258</v>
+        <v>46252</v>
       </c>
       <c r="I57">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J57">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="58">
@@ -2073,31 +2073,31 @@
         <v>49</v>
       </c>
       <c r="B58" t="str">
-        <v>28.09.2026</v>
+        <v>25.09.2026</v>
       </c>
       <c r="C58" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D58" t="str">
-        <v>SECRET GARDENS, Лозенец; SLOW LIFE, Владая; ДНСК</v>
+        <v>SECRET GARDENS, Лозенец; KRISTA, Кръстова вада; НАП, Централно управление</v>
       </c>
       <c r="E58" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F58" t="str">
-        <v>Контрол на доставка на материали; Контрол на СМР; Подаване на документи</v>
+        <v>Среща с подизпълнител; Приемане на изпълнени СМР; Подаване на документи</v>
       </c>
       <c r="G58">
-        <v>46258</v>
+        <v>46252</v>
       </c>
       <c r="H58">
-        <v>46294</v>
+        <v>46274</v>
       </c>
       <c r="I58">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="J58">
-        <v>2.09</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="59">
@@ -2105,31 +2105,31 @@
         <v>50</v>
       </c>
       <c r="B59" t="str">
-        <v>28.09.2026</v>
+        <v>25.09.2026</v>
       </c>
       <c r="C59" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D59" t="str">
-        <v>UPTOWN SQUARE, Лозенец; SLOW LIFE, Владая; Агенция по вписванията</v>
+        <v>SREDA, Манастирски ливади-изток; SONATA, ул. Филип Аврамов; НАП, Централно управление</v>
       </c>
       <c r="E59" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F59" t="str">
-        <v>Контрол на СМР; Приемане на изпълнени СМР; Среща в администрацията</v>
+        <v>Приемане на изпълнени СМР; Среща с клиент; Подаване на документи</v>
       </c>
       <c r="G59">
-        <v>46294</v>
+        <v>46274</v>
       </c>
       <c r="H59">
-        <v>46330</v>
+        <v>46298</v>
       </c>
       <c r="I59">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="J59">
-        <v>2.09</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="60">
@@ -2137,31 +2137,31 @@
         <v>51</v>
       </c>
       <c r="B60" t="str">
-        <v>28.09.2026</v>
+        <v>25.09.2026</v>
       </c>
       <c r="C60" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D60" t="str">
-        <v>MONA 6, Манастирски ливади-изток; Столична община, ул. Московска 33; МРРБ, ул. Св. св. Кирил и Методий 17</v>
+        <v>Посещение при клиент</v>
       </c>
       <c r="E60" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F60" t="str">
-        <v>Контрол на СМР; Среща в администрацията; Подаване на документи</v>
+        <v>Оглед при клиент</v>
       </c>
       <c r="G60">
-        <v>46330</v>
+        <v>46298</v>
       </c>
       <c r="H60">
-        <v>46352</v>
+        <v>46313</v>
       </c>
       <c r="I60">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J60">
-        <v>1.28</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="61">
@@ -2169,31 +2169,31 @@
         <v>52</v>
       </c>
       <c r="B61" t="str">
-        <v>29.09.2026</v>
+        <v>28.09.2026</v>
       </c>
       <c r="C61" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D61" t="str">
-        <v>UPTOWN SQUARE, Лозенец; Съдебна палата, бул. Витоша 2</v>
+        <v>MONA 5, Манастирски ливади-изток; AVIVA Living, Възраждане; Столична община, ул. Московска 33</v>
       </c>
       <c r="E61" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F61" t="str">
-        <v>Среща с клиент; Получаване на документи</v>
+        <v>Контрол на СМР; Оглед на обект; Подаване на документи</v>
       </c>
       <c r="G61">
-        <v>46352</v>
+        <v>46313</v>
       </c>
       <c r="H61">
-        <v>46365</v>
+        <v>46337</v>
       </c>
       <c r="I61">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="J61">
-        <v>0.75</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="62">
@@ -2207,25 +2207,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D62" t="str">
-        <v>SECRET GARDENS, Лозенец; SONATA, ул. Филип Аврамов; НАП, Централно управление</v>
+        <v>SREDA, Манастирски ливади-изток; SLOW LIFE, Владая; МРРБ, ул. Св. св. Кирил и Методий 17</v>
       </c>
       <c r="E62" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F62" t="str">
-        <v>Контрол на СМР; Приемане на изпълнени СМР; Получаване на документи</v>
+        <v>Контрол на доставка на материали; Среща с подизпълнител; Среща в администрацията</v>
       </c>
       <c r="G62">
-        <v>46365</v>
+        <v>46337</v>
       </c>
       <c r="H62">
-        <v>46385</v>
+        <v>46375</v>
       </c>
       <c r="I62">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="J62">
-        <v>1.16</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="63">
@@ -2239,25 +2239,25 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D63" t="str">
-        <v>Посещение при клиент</v>
+        <v>SREDA, Манастирски ливади-изток; Столична община, ул. Московска 33; Съдебна палата, бул. Витоша 2</v>
       </c>
       <c r="E63" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F63" t="str">
-        <v>Среща с клиент</v>
+        <v>Среща с клиент; Получаване на документи; Среща в администрацията</v>
       </c>
       <c r="G63">
-        <v>46385</v>
+        <v>46375</v>
       </c>
       <c r="H63">
-        <v>46424</v>
+        <v>46397</v>
       </c>
       <c r="I63">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="J63">
-        <v>2.26</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="64">
@@ -2265,31 +2265,31 @@
         <v>55</v>
       </c>
       <c r="B64" t="str">
-        <v>30.09.2026</v>
+        <v>29.09.2026</v>
       </c>
       <c r="C64" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D64" t="str">
-        <v>SREDA, Манастирски ливади-изток; AVIVA Living, Възраждане; НАП, Централно управление</v>
+        <v>Посещение при клиент</v>
       </c>
       <c r="E64" t="str">
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F64" t="str">
-        <v>Контрол на СМР; Среща с клиент; Получаване на документи</v>
+        <v>Оглед при клиент</v>
       </c>
       <c r="G64">
-        <v>46424</v>
+        <v>46397</v>
       </c>
       <c r="H64">
-        <v>46449</v>
+        <v>46435</v>
       </c>
       <c r="I64">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="J64">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="65">
@@ -2303,106 +2303,138 @@
         <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="D65" t="str">
+        <v>KRISTA, Кръстова вада; НАП, Централно управление</v>
+      </c>
+      <c r="E65" t="str">
+        <v>BLD – офис, ул. „Тинтява“ 126, София</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Контрол на доставка на материали; Подаване на документи</v>
+      </c>
+      <c r="G65">
+        <v>46435</v>
+      </c>
+      <c r="H65">
+        <v>46455</v>
+      </c>
+      <c r="I65">
+        <v>20</v>
+      </c>
+      <c r="J65">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>57</v>
+      </c>
+      <c r="B66" t="str">
+        <v>30.09.2026</v>
+      </c>
+      <c r="C66" t="str">
+        <v>BLD – офис, ул. „Тинтява“ 126, София</v>
+      </c>
+      <c r="D66" t="str">
         <v>Посещение при клиент</v>
       </c>
-      <c r="E65" t="str">
-        <v>BLD – офис, ул. „Тинтява“ 126, София</v>
-      </c>
-      <c r="F65" t="str">
-        <v>Среща с клиент</v>
-      </c>
-      <c r="G65">
-        <v>46449</v>
-      </c>
-      <c r="H65">
-        <v>46480</v>
-      </c>
-      <c r="I65">
-        <v>31</v>
-      </c>
-      <c r="J65">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v/>
-      </c>
-      <c r="B66" t="str">
-        <v/>
-      </c>
-      <c r="C66" t="str">
-        <v>ОБЩО за периода</v>
-      </c>
-      <c r="D66" t="str">
-        <v/>
-      </c>
       <c r="E66" t="str">
-        <v/>
+        <v>BLD – офис, ул. „Тинтява“ 126, София</v>
       </c>
       <c r="F66" t="str">
-        <v/>
+        <v>Оглед при клиент</v>
       </c>
       <c r="G66">
-        <v>45000</v>
+        <v>46455</v>
       </c>
       <c r="H66">
         <v>46480</v>
       </c>
       <c r="I66">
+        <v>25</v>
+      </c>
+      <c r="J66">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v/>
+      </c>
+      <c r="B67" t="str">
+        <v/>
+      </c>
+      <c r="C67" t="str">
+        <v>ОБЩО за периода</v>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67">
+        <v>45000</v>
+      </c>
+      <c r="H67">
+        <v>46480</v>
+      </c>
+      <c r="I67">
         <v>1480</v>
       </c>
-      <c r="J66">
-        <v>85.82</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>Зареждания: дата</v>
-      </c>
-      <c r="B68" t="str">
-        <v>Количество, л</v>
-      </c>
-      <c r="C68" t="str">
-        <v>№ на фактура</v>
+      <c r="J67">
+        <v>85.84</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>08.09.2026</v>
-      </c>
-      <c r="B69">
-        <v>42.5</v>
+        <v>Зареждания: дата</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Количество, л</v>
       </c>
       <c r="C69" t="str">
-        <v>F-0012345</v>
+        <v>№ на фактура</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
+        <v>08.09.2026</v>
+      </c>
+      <c r="B70">
+        <v>42.5</v>
+      </c>
+      <c r="C70" t="str">
+        <v>F-0012345</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
         <v>22.09.2026</v>
       </c>
-      <c r="B70">
+      <c r="B71">
         <v>38.1</v>
       </c>
-      <c r="C70" t="str">
+      <c r="C71" t="str">
         <v>F-0012871</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="str">
+    <row r="73">
+      <c r="A73" t="str">
         <v>Водач: ____________</v>
       </c>
-      <c r="B72" t="str">
+      <c r="B73" t="str">
         <v/>
       </c>
-      <c r="C72" t="str">
+      <c r="C73" t="str">
         <v>Одобрил: ____________ Димитър Бончев Савов</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J72"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J73"/>
   </ignoredErrors>
 </worksheet>
 </file>